--- a/tobuy.xlsx
+++ b/tobuy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xGino/GitHub/PERSONAL/xgino/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gin/GitHub/Gin/xgino/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC89B30-7C7D-A740-85D7-4273B730670A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790A161C-4749-9341-B8DA-2F234DB3290F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="3820" windowWidth="21600" windowHeight="11320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,54 +36,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Product</t>
   </si>
   <si>
-    <t>Poster rast</t>
-  </si>
-  <si>
-    <t>Poster Business</t>
-  </si>
-  <si>
-    <t>Kamer lamp Smart</t>
-  </si>
-  <si>
-    <t>Muis draadloos</t>
-  </si>
-  <si>
-    <t>100w charger extener on desk</t>
-  </si>
-  <si>
-    <t>Usb PC extender desk</t>
-  </si>
-  <si>
-    <t>Neo Logo board</t>
-  </si>
-  <si>
-    <t>Tesla model s</t>
-  </si>
-  <si>
-    <t>pet</t>
-  </si>
-  <si>
     <t>est price</t>
   </si>
   <si>
-    <t>drone cam build</t>
-  </si>
-  <si>
-    <t>Macbook pro 16 inch</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> camera</t>
-  </si>
-  <si>
-    <t>Electric Bike Scooter Funn</t>
-  </si>
-  <si>
-    <t>?</t>
+    <t>Drone build Camera</t>
+  </si>
+  <si>
+    <t>Tesla or Honda Civic</t>
+  </si>
+  <si>
+    <t>Gopro</t>
+  </si>
+  <si>
+    <t>House Rotterdam</t>
+  </si>
+  <si>
+    <t>Robot arm Build</t>
   </si>
 </sst>
 </file>
@@ -410,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:C15"/>
+  <dimension ref="B2:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.83203125" bestFit="1" customWidth="1"/>
@@ -421,39 +394,39 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>80</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
@@ -461,71 +434,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
